--- a/research/traditional_assets/database/data/ireland/ireland_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_oil_gas_production_and_exploration.xlsx
@@ -588,34 +588,37 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0437</v>
+        <v>0.1425</v>
+      </c>
+      <c r="E2">
+        <v>0.276</v>
       </c>
       <c r="G2">
-        <v>-2.425538277511962</v>
+        <v>-2.461887935386168</v>
       </c>
       <c r="H2">
-        <v>-2.425538277511962</v>
+        <v>-2.461887935386168</v>
       </c>
       <c r="I2">
-        <v>-4.327419121905475</v>
+        <v>-3.409052667003197</v>
       </c>
       <c r="J2">
-        <v>-4.327419121905475</v>
+        <v>-3.389869321856123</v>
       </c>
       <c r="K2">
-        <v>-14.691</v>
+        <v>3.790999999999999</v>
       </c>
       <c r="L2">
-        <v>-4.393241626794259</v>
+        <v>0.6378933198721183</v>
       </c>
       <c r="M2">
-        <v>0.748</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.003212920407199003</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.05091552651283098</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,82 +627,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0.748</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>16.956</v>
+        <v>26.321</v>
       </c>
       <c r="V2">
-        <v>0.07283192302736137</v>
+        <v>0.06792340842816959</v>
       </c>
       <c r="W2">
-        <v>-0.07694117647058824</v>
+        <v>-0.008415841584158416</v>
       </c>
       <c r="X2">
-        <v>0.07362365352030338</v>
+        <v>0.1226321919444638</v>
       </c>
       <c r="Y2">
-        <v>-0.1505648299908916</v>
+        <v>-0.1310480335286222</v>
       </c>
       <c r="Z2">
-        <v>0.01859870672491418</v>
+        <v>0.01948141349242772</v>
       </c>
       <c r="AA2">
-        <v>-0.07256494880257258</v>
+        <v>-0.1401232565682776</v>
       </c>
       <c r="AB2">
-        <v>0.0736125209267337</v>
+        <v>0.1226321919444638</v>
       </c>
       <c r="AC2">
-        <v>-0.1463209057520884</v>
+        <v>-0.2627554485127415</v>
       </c>
       <c r="AD2">
-        <v>9.130000000000001</v>
+        <v>3.44</v>
       </c>
       <c r="AE2">
-        <v>0.01444771825953819</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>9.144447718259539</v>
+        <v>3.44</v>
       </c>
       <c r="AG2">
-        <v>-7.811552281740461</v>
+        <v>-22.881</v>
       </c>
       <c r="AH2">
-        <v>0.03779408812070139</v>
+        <v>0.008799079166133778</v>
       </c>
       <c r="AI2">
-        <v>0.04404533412177987</v>
+        <v>0.01014976808960121</v>
       </c>
       <c r="AJ2">
-        <v>-0.03471824966331322</v>
+        <v>-0.06275145421784882</v>
       </c>
       <c r="AK2">
-        <v>-0.04097144592975904</v>
+        <v>-0.07319507490331185</v>
       </c>
       <c r="AL2">
-        <v>0.763</v>
+        <v>0.271</v>
       </c>
       <c r="AM2">
-        <v>-2.31</v>
+        <v>-14.848</v>
       </c>
       <c r="AN2">
-        <v>-0.9129087091290872</v>
+        <v>-0.2838283828382839</v>
       </c>
       <c r="AO2">
-        <v>-18.98165137614679</v>
+        <v>-74.76014760147602</v>
       </c>
       <c r="AP2">
-        <v>0.781077120462</v>
+        <v>1.887871287128713</v>
       </c>
       <c r="AQ2">
-        <v>6.26969696969697</v>
+        <v>1.364493534482759</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clontarf Energy plc (AIM:CLON)</t>
+          <t>Lansdowne Oil &amp; Gas plc (AIM:LOGP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.486</v>
+        <v>-0.17</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,61 +743,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.649</v>
+        <v>0.215</v>
       </c>
       <c r="V3">
-        <v>0.2394833948339483</v>
+        <v>0.0402621722846442</v>
       </c>
       <c r="W3">
-        <v>1.729537366548042</v>
+        <v>-0.008415841584158416</v>
       </c>
       <c r="X3">
-        <v>0.07360946335796577</v>
+        <v>0.1402149737755124</v>
       </c>
       <c r="Y3">
-        <v>1.655927903190077</v>
+        <v>-0.1486308153596708</v>
       </c>
       <c r="Z3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.941860465116279</v>
+        <v>-0.005070314742179279</v>
       </c>
       <c r="AB3">
-        <v>0.07360946335796577</v>
+        <v>0.1238688539535114</v>
       </c>
       <c r="AC3">
-        <v>0.8682510017583132</v>
+        <v>-0.1289391686956907</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG3">
-        <v>-0.649</v>
+        <v>1.065</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.1933534743202417</v>
       </c>
       <c r="AI3">
-        <v>-0</v>
+        <v>0.06673618352450469</v>
       </c>
       <c r="AJ3">
-        <v>-0.3148956817079088</v>
+        <v>0.1662763466042155</v>
       </c>
       <c r="AK3">
-        <v>0.9460641399416909</v>
+        <v>0.05615607698391774</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.064</v>
+      </c>
+      <c r="AO3">
+        <v>-1.65625</v>
+      </c>
+      <c r="AQ3">
+        <v>-1.65625</v>
       </c>
     </row>
     <row r="4">
@@ -808,7 +814,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lansdowne Oil &amp; Gas plc (AIM:LOGP)</t>
+          <t>Barryroe Offshore Energy plc (ISE:BEY)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -817,7 +823,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-0.499</v>
+        <v>-0.555</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -841,67 +847,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.6840000000000001</v>
+        <v>2.29</v>
       </c>
       <c r="V4">
-        <v>0.1105008077544427</v>
+        <v>0.0571072319201995</v>
       </c>
       <c r="W4">
-        <v>-0.02851428571428571</v>
+        <v>-0.008258928571428572</v>
       </c>
       <c r="X4">
-        <v>0.08510576946606364</v>
+        <v>0.1226321919444638</v>
       </c>
       <c r="Y4">
-        <v>-0.1136200551803494</v>
+        <v>-0.1308911205158924</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.02294045130514016</v>
+        <v>-0.02544529262086514</v>
       </c>
       <c r="AB4">
-        <v>0.07514403485503117</v>
+        <v>0.1226321919444638</v>
       </c>
       <c r="AC4">
-        <v>-0.09808448616017133</v>
+        <v>-0.1480774845653289</v>
       </c>
       <c r="AD4">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.7059999999999998</v>
+        <v>-2.29</v>
       </c>
       <c r="AH4">
-        <v>0.183377308707124</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.06438165817508106</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.1023781902552204</v>
+        <v>-0.06056598783390637</v>
       </c>
       <c r="AK4">
-        <v>0.03377020950923179</v>
+        <v>-0.03412308150797199</v>
       </c>
       <c r="AL4">
-        <v>0.073</v>
+        <v>0.068</v>
       </c>
       <c r="AM4">
-        <v>0.073</v>
+        <v>0.068</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
       </c>
       <c r="AO4">
-        <v>-5.863013698630137</v>
+        <v>-23.52941176470588</v>
+      </c>
+      <c r="AP4">
+        <v>1.846774193548387</v>
       </c>
       <c r="AQ4">
-        <v>-5.863013698630137</v>
+        <v>-23.52941176470588</v>
       </c>
     </row>
     <row r="5">
@@ -912,7 +924,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Providence Resources P.l.c. (ISE:PZQA)</t>
+          <t>San Leon Energy plc (AIM:SLE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -920,8 +932,29 @@
           <t>Oil/Gas (Production and Exploration)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.8959999999999999</v>
+      </c>
+      <c r="E5">
+        <v>0.276</v>
+      </c>
+      <c r="G5">
+        <v>-1.102389078498293</v>
+      </c>
+      <c r="H5">
+        <v>-1.102389078498293</v>
+      </c>
+      <c r="I5">
+        <v>-0.9692832764505118</v>
+      </c>
+      <c r="J5">
+        <v>-0.9311029717805709</v>
+      </c>
       <c r="K5">
-        <v>0.613</v>
+        <v>23.7</v>
+      </c>
+      <c r="L5">
+        <v>4.044368600682594</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -945,67 +978,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>4.32</v>
+        <v>0.267</v>
       </c>
       <c r="V5">
-        <v>0.1035971223021583</v>
+        <v>0.001461412151067324</v>
       </c>
       <c r="W5">
-        <v>0.01040747028862479</v>
+        <v>0.147940074906367</v>
       </c>
       <c r="X5">
-        <v>0.07362365352030338</v>
+        <v>0.1234994215163031</v>
       </c>
       <c r="Y5">
-        <v>-0.06321618323167859</v>
+        <v>0.02444065339006397</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>0.03885683973211326</v>
       </c>
       <c r="AA5">
-        <v>-0.06332522682490051</v>
+        <v>-0.03617971894857201</v>
       </c>
       <c r="AB5">
-        <v>0.0736125209267337</v>
+        <v>0.122706924501364</v>
       </c>
       <c r="AC5">
-        <v>-0.1369377477516342</v>
+        <v>-0.158886643449936</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE5">
-        <v>0.01155817460763056</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.01155817460763056</v>
+        <v>2.16</v>
       </c>
       <c r="AG5">
-        <v>-4.30844182539237</v>
+        <v>1.893</v>
       </c>
       <c r="AH5">
-        <v>0.0002770976466342301</v>
+        <v>0.01168451801363194</v>
       </c>
       <c r="AI5">
-        <v>0.0001719670681879416</v>
+        <v>0.01276143211627083</v>
       </c>
       <c r="AJ5">
-        <v>-0.1152249875566353</v>
+        <v>0.01025499341795193</v>
       </c>
       <c r="AK5">
-        <v>-0.06850588458041888</v>
+        <v>0.01120164740551384</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-14.982</v>
       </c>
       <c r="AN5">
-        <v>-0</v>
+        <v>-0.4052532833020638</v>
+      </c>
+      <c r="AO5">
+        <v>-48.13559322033898</v>
       </c>
       <c r="AP5">
-        <v>1.664776594046511</v>
+        <v>-0.3551594746716698</v>
+      </c>
+      <c r="AQ5">
+        <v>0.3791216126017888</v>
       </c>
     </row>
     <row r="6">
@@ -1016,7 +1055,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aminex PLC (LSE:AEX)</t>
+          <t>Falcon Oil &amp; Gas Ltd. (TSXV:FO)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1024,26 +1063,8 @@
           <t>Oil/Gas (Production and Exploration)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>-0.173</v>
-      </c>
-      <c r="G6">
-        <v>-13.05882352941176</v>
-      </c>
-      <c r="H6">
-        <v>-13.05882352941176</v>
-      </c>
-      <c r="I6">
-        <v>-20.17647058823529</v>
-      </c>
-      <c r="J6">
-        <v>-20.17647058823529</v>
-      </c>
       <c r="K6">
-        <v>-6.58</v>
-      </c>
-      <c r="L6">
-        <v>-38.70588235294117</v>
+        <v>-4.76</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1067,73 +1088,70 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.491</v>
+        <v>16.9</v>
       </c>
       <c r="V6">
-        <v>0.01604575163398693</v>
+        <v>0.1688311688311688</v>
       </c>
       <c r="W6">
-        <v>-0.1433551198257081</v>
+        <v>-0.118407960199005</v>
       </c>
       <c r="X6">
-        <v>0.07381023112439015</v>
+        <v>0.1226321919444638</v>
       </c>
       <c r="Y6">
-        <v>-0.2171653509500982</v>
+        <v>-0.2410401521434687</v>
       </c>
       <c r="Z6">
-        <v>0.003596513497503597</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>-0.07256494880257258</v>
+        <v>-0.1401232565682776</v>
       </c>
       <c r="AB6">
-        <v>0.0737559569495158</v>
+        <v>0.1226321919444638</v>
       </c>
       <c r="AC6">
-        <v>-0.1463209057520884</v>
+        <v>-0.2627554485127415</v>
       </c>
       <c r="AD6">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>-0.371</v>
+        <v>-16.9</v>
       </c>
       <c r="AH6">
-        <v>0.00390625</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.003006012024048097</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.0122729828972179</v>
+        <v>-0.203125</v>
       </c>
       <c r="AK6">
-        <v>-0.009409318014659262</v>
+        <v>-0.5633333333333332</v>
       </c>
       <c r="AL6">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>0.13</v>
+        <v>-0.019</v>
       </c>
       <c r="AN6">
-        <v>-0.04316546762589928</v>
-      </c>
-      <c r="AO6">
-        <v>-26.38461538461538</v>
+        <v>-0</v>
       </c>
       <c r="AP6">
-        <v>0.133453237410072</v>
+        <v>4.1320293398533</v>
       </c>
       <c r="AQ6">
-        <v>-26.38461538461538</v>
+        <v>227.3684210526316</v>
       </c>
     </row>
     <row r="7">
@@ -1144,7 +1162,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Falcon Oil &amp; Gas Ltd. (TSXV:FO)</t>
+          <t>Aminex PLC (LSE:AEX)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1153,25 +1171,25 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0437</v>
+        <v>-0.611</v>
       </c>
       <c r="G7">
-        <v>-510</v>
+        <v>-19.63855421686747</v>
       </c>
       <c r="H7">
-        <v>-510</v>
+        <v>-19.63855421686747</v>
       </c>
       <c r="I7">
-        <v>-797.5</v>
+        <v>-88.43373493975903</v>
       </c>
       <c r="J7">
-        <v>-797.5</v>
+        <v>-88.43373493975903</v>
       </c>
       <c r="K7">
-        <v>-3.27</v>
+        <v>-8.23</v>
       </c>
       <c r="L7">
-        <v>-817.5</v>
+        <v>-99.1566265060241</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1195,31 +1213,31 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>9.369999999999999</v>
+        <v>6.39</v>
       </c>
       <c r="V7">
-        <v>0.09436052366565961</v>
+        <v>0.1172477064220183</v>
       </c>
       <c r="W7">
-        <v>-0.07694117647058824</v>
+        <v>-0.20678391959799</v>
       </c>
       <c r="X7">
-        <v>0.07360946335796577</v>
+        <v>0.1226321919444638</v>
       </c>
       <c r="Y7">
-        <v>-0.150550639828554</v>
+        <v>-0.3294161115424538</v>
       </c>
       <c r="Z7">
-        <v>0.0001290322580645161</v>
+        <v>0.00210504958279439</v>
       </c>
       <c r="AA7">
-        <v>-0.1029032258064516</v>
+        <v>-0.1861573968398894</v>
       </c>
       <c r="AB7">
-        <v>0.07360946335796577</v>
+        <v>0.1226321919444638</v>
       </c>
       <c r="AC7">
-        <v>-0.1765126891644174</v>
+        <v>-0.3087895887843533</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1231,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-9.369999999999999</v>
+        <v>-6.39</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1240,25 +1258,28 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.1041921494495719</v>
+        <v>-0.1328206194138433</v>
       </c>
       <c r="AK7">
-        <v>-0.2971772914684427</v>
+        <v>-0.2210307851954341</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="AM7">
-        <v>-0.003</v>
+        <v>0.021</v>
       </c>
       <c r="AN7">
         <v>-0</v>
       </c>
+      <c r="AO7">
+        <v>-349.5238095238095</v>
+      </c>
       <c r="AP7">
-        <v>3.16554054054054</v>
+        <v>4.376712328767123</v>
       </c>
       <c r="AQ7">
-        <v>1063.333333333333</v>
+        <v>-349.5238095238095</v>
       </c>
     </row>
     <row r="8">
@@ -1269,7 +1290,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PetroNeft Resources plc (ISE:P8ET)</t>
+          <t>Petrel Resources Plc (AIM:PET)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1277,35 +1298,17 @@
           <t>Oil/Gas (Production and Exploration)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.0455</v>
-      </c>
-      <c r="G8">
-        <v>-0.2280757097791798</v>
-      </c>
-      <c r="H8">
-        <v>-0.2280757097791798</v>
-      </c>
-      <c r="I8">
-        <v>-0.9235261541736219</v>
-      </c>
-      <c r="J8">
-        <v>-0.9235261541736219</v>
-      </c>
       <c r="K8">
-        <v>-4.03</v>
-      </c>
-      <c r="L8">
-        <v>-1.271293375394322</v>
+        <v>-0.314</v>
       </c>
       <c r="M8">
-        <v>0.748</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.01532786885245902</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>-0.1856079404466501</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <v>-0</v>
@@ -1317,79 +1320,64 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>0.748</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1.14</v>
+        <v>0.031</v>
       </c>
       <c r="V8">
-        <v>0.02336065573770492</v>
+        <v>0.01033333333333333</v>
       </c>
       <c r="W8">
-        <v>-0.1767543859649123</v>
+        <v>-0.6193293885601577</v>
       </c>
       <c r="X8">
-        <v>0.08160658998463803</v>
+        <v>0.1226321919444638</v>
       </c>
       <c r="Y8">
-        <v>-0.2583609759495503</v>
+        <v>-0.7419615805046216</v>
       </c>
       <c r="Z8">
-        <v>0.1192630990732275</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>-0.1101425912219254</v>
+        <v>-1.531707317073171</v>
       </c>
       <c r="AB8">
-        <v>0.07510022324872172</v>
+        <v>0.1226321919444638</v>
       </c>
       <c r="AC8">
-        <v>-0.1852428144706471</v>
+        <v>-1.654339509017634</v>
       </c>
       <c r="AD8">
-        <v>7.62</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>0.002889543651907639</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>7.622889543651908</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>6.482889543651909</v>
+        <v>-0.031</v>
       </c>
       <c r="AH8">
-        <v>0.1351027855061272</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.2031530523464588</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>0.1172675595860986</v>
+        <v>-0.01044122600202088</v>
       </c>
       <c r="AK8">
-        <v>0.178185120120099</v>
+        <v>-0.3009708737864077</v>
       </c>
       <c r="AL8">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>-2.51</v>
-      </c>
-      <c r="AN8">
-        <v>-20.42895442359249</v>
-      </c>
-      <c r="AO8">
-        <v>-5.232142857142857</v>
-      </c>
-      <c r="AP8">
-        <v>-17.38040092131879</v>
-      </c>
-      <c r="AQ8">
-        <v>1.167330677290837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1400,7 +1388,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Petrel Resources Plc (AIM:PET)</t>
+          <t>Clontarf Energy plc (AIM:CLON)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1409,7 +1397,7 @@
         </is>
       </c>
       <c r="K9">
-        <v>-0.439</v>
+        <v>-5.88</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1433,31 +1421,22 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.302</v>
+        <v>0.228</v>
       </c>
       <c r="V9">
-        <v>0.08603988603988605</v>
+        <v>0.1288135593220339</v>
       </c>
       <c r="W9">
-        <v>-0.4943693693693694</v>
+        <v>158.9189189189189</v>
       </c>
       <c r="X9">
-        <v>0.07360946335796577</v>
+        <v>0.1226321919444638</v>
       </c>
       <c r="Y9">
-        <v>-0.5679788327273352</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>-1.025700934579439</v>
+        <v>158.7962867269745</v>
       </c>
       <c r="AB9">
-        <v>0.07360946335796577</v>
-      </c>
-      <c r="AC9">
-        <v>-1.099310397937405</v>
+        <v>0.1226321919444638</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -1469,31 +1448,25 @@
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>-0.302</v>
+        <v>-0.228</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9">
-        <v>-0.09413965087281796</v>
+        <v>-0.1478599221789883</v>
       </c>
       <c r="AK9">
-        <v>-1.473170731707317</v>
+        <v>0.1542625169147497</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
         <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>-0</v>
-      </c>
-      <c r="AP9">
-        <v>0.2323076923076923</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ireland/ireland_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_oil_gas_production_and_exploration.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,28 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1425</v>
-      </c>
-      <c r="E2">
-        <v>0.276</v>
+        <v>-0.451</v>
       </c>
       <c r="G2">
-        <v>-2.461887935386168</v>
+        <v>0.418325923062053</v>
       </c>
       <c r="H2">
-        <v>-2.461887935386168</v>
+        <v>0.418325923062053</v>
       </c>
       <c r="I2">
-        <v>-3.409052667003197</v>
+        <v>-0.2243056897996005</v>
       </c>
       <c r="J2">
-        <v>-3.389869321856123</v>
+        <v>-0.2056135489829671</v>
       </c>
       <c r="K2">
-        <v>3.790999999999999</v>
+        <v>-28.474</v>
       </c>
       <c r="L2">
-        <v>0.6378933198721183</v>
+        <v>-1.834783169018622</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>26.321</v>
+        <v>20.386</v>
       </c>
       <c r="V2">
-        <v>0.06792340842816959</v>
+        <v>0.1150386547034592</v>
       </c>
       <c r="W2">
-        <v>-0.008415841584158416</v>
+        <v>-0.09128619256098011</v>
       </c>
       <c r="X2">
-        <v>0.1226321919444638</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="Y2">
-        <v>-0.1310480335286222</v>
+        <v>-0.1827616353128908</v>
       </c>
       <c r="Z2">
-        <v>0.01948141349242772</v>
+        <v>0.1490949965413881</v>
       </c>
       <c r="AA2">
-        <v>-0.1401232565682776</v>
+        <v>-0.1327676335762511</v>
       </c>
       <c r="AB2">
-        <v>0.1226321919444638</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="AC2">
-        <v>-0.2627554485127415</v>
+        <v>-0.2242430763281618</v>
       </c>
       <c r="AD2">
-        <v>3.44</v>
+        <v>3.06</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.44</v>
+        <v>3.06</v>
       </c>
       <c r="AG2">
-        <v>-22.881</v>
+        <v>-17.326</v>
       </c>
       <c r="AH2">
-        <v>0.008799079166133778</v>
+        <v>0.01697453819271093</v>
       </c>
       <c r="AI2">
-        <v>0.01014976808960121</v>
+        <v>0.02866242038216561</v>
       </c>
       <c r="AJ2">
-        <v>-0.06275145421784882</v>
+        <v>-0.1083660653974131</v>
       </c>
       <c r="AK2">
-        <v>-0.07319507490331185</v>
+        <v>-0.2005927709727464</v>
       </c>
       <c r="AL2">
-        <v>0.271</v>
+        <v>0.168</v>
       </c>
       <c r="AM2">
-        <v>-14.848</v>
+        <v>-1.345</v>
       </c>
       <c r="AN2">
-        <v>-0.2838283828382839</v>
+        <v>0.7200000000000002</v>
       </c>
       <c r="AO2">
-        <v>-74.76014760147602</v>
+        <v>-20.72023809523809</v>
       </c>
       <c r="AP2">
-        <v>1.887871287128713</v>
+        <v>-4.076705882352942</v>
       </c>
       <c r="AQ2">
-        <v>1.364493534482759</v>
+        <v>2.588104089219331</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lansdowne Oil &amp; Gas plc (AIM:LOGP)</t>
+          <t>United Oil &amp; Gas Plc (AIM:UOG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,8 +715,23 @@
           <t>Oil/Gas (Production and Exploration)</t>
         </is>
       </c>
+      <c r="G3">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="H3">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="I3">
+        <v>0.3616883116883117</v>
+      </c>
+      <c r="J3">
+        <v>0.1808441558441559</v>
+      </c>
       <c r="K3">
-        <v>-0.17</v>
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="L3">
+        <v>0.03675324675324675</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -728,7 +740,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -737,73 +749,76 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.215</v>
+        <v>0.554</v>
       </c>
       <c r="V3">
-        <v>0.0402621722846442</v>
+        <v>0.1103585657370518</v>
       </c>
       <c r="W3">
-        <v>-0.008415841584158416</v>
+        <v>0.0212781954887218</v>
       </c>
       <c r="X3">
-        <v>0.1402149737755124</v>
+        <v>0.1078184710559149</v>
       </c>
       <c r="Y3">
-        <v>-0.1486308153596708</v>
+        <v>-0.08654027556719308</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.5744125326370757</v>
       </c>
       <c r="AA3">
-        <v>-0.005070314742179279</v>
+        <v>0.1038791495710556</v>
       </c>
       <c r="AB3">
-        <v>0.1238688539535114</v>
+        <v>0.09335047988202637</v>
       </c>
       <c r="AC3">
-        <v>-0.1289391686956907</v>
+        <v>0.0105286696890292</v>
       </c>
       <c r="AD3">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="AG3">
-        <v>1.065</v>
+        <v>1.226</v>
       </c>
       <c r="AH3">
-        <v>0.1933534743202417</v>
+        <v>0.261764705882353</v>
       </c>
       <c r="AI3">
-        <v>0.06673618352450469</v>
+        <v>0.06017579445571332</v>
       </c>
       <c r="AJ3">
-        <v>0.1662763466042155</v>
+        <v>0.1962856227985911</v>
       </c>
       <c r="AK3">
-        <v>0.05615607698391774</v>
+        <v>0.0422379935230483</v>
       </c>
       <c r="AL3">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.064</v>
-      </c>
-      <c r="AO3">
-        <v>-1.65625</v>
+        <v>-1.33</v>
+      </c>
+      <c r="AN3">
+        <v>0.1953896816684962</v>
+      </c>
+      <c r="AP3">
+        <v>0.1345773874862788</v>
       </c>
       <c r="AQ3">
-        <v>-1.65625</v>
+        <v>-4.18796992481203</v>
       </c>
     </row>
     <row r="4">
@@ -814,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barryroe Offshore Energy plc (ISE:BEY)</t>
+          <t>Lansdowne Oil &amp; Gas plc (AIM:LOGP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -823,7 +838,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-0.555</v>
+        <v>-20.7</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -847,73 +862,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.29</v>
+        <v>0.052</v>
       </c>
       <c r="V4">
-        <v>0.0571072319201995</v>
+        <v>0.03249999999999999</v>
       </c>
       <c r="W4">
-        <v>-0.008258928571428572</v>
+        <v>-1.156424581005587</v>
       </c>
       <c r="X4">
-        <v>0.1226321919444638</v>
+        <v>0.1283482526782482</v>
       </c>
       <c r="Y4">
-        <v>-0.1308911205158924</v>
+        <v>-1.284772833683835</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.02544529262086514</v>
+        <v>-0.01376219351436857</v>
       </c>
       <c r="AB4">
-        <v>0.1226321919444638</v>
+        <v>0.09465902639355525</v>
       </c>
       <c r="AC4">
-        <v>-0.1480774845653289</v>
+        <v>-0.1084212199079238</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG4">
-        <v>-2.29</v>
+        <v>1.228</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.4444444444444445</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>-12.80000000000002</v>
       </c>
       <c r="AJ4">
-        <v>-0.06056598783390637</v>
+        <v>0.4342291371994342</v>
       </c>
       <c r="AK4">
-        <v>-0.03412308150797199</v>
+        <v>-8.078947368421057</v>
       </c>
       <c r="AL4">
-        <v>0.068</v>
+        <v>0.168</v>
       </c>
       <c r="AM4">
-        <v>0.068</v>
-      </c>
-      <c r="AN4">
-        <v>-0</v>
+        <v>0.168</v>
       </c>
       <c r="AO4">
-        <v>-23.52941176470588</v>
-      </c>
-      <c r="AP4">
-        <v>1.846774193548387</v>
+        <v>-1.553571428571429</v>
       </c>
       <c r="AQ4">
-        <v>-23.52941176470588</v>
+        <v>-1.553571428571429</v>
       </c>
     </row>
     <row r="5">
@@ -924,7 +933,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>San Leon Energy plc (AIM:SLE)</t>
+          <t>Aminex PLC (LSE:AEX)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -933,28 +942,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.8959999999999999</v>
-      </c>
-      <c r="E5">
-        <v>0.276</v>
+        <v>-0.451</v>
       </c>
       <c r="G5">
-        <v>-1.102389078498293</v>
+        <v>-26.5546218487395</v>
       </c>
       <c r="H5">
-        <v>-1.102389078498293</v>
+        <v>-26.5546218487395</v>
       </c>
       <c r="I5">
-        <v>-0.9692832764505118</v>
+        <v>-31.26050420168067</v>
       </c>
       <c r="J5">
-        <v>-0.9311029717805709</v>
+        <v>-31.26050420168067</v>
       </c>
       <c r="K5">
-        <v>23.7</v>
+        <v>-3.74</v>
       </c>
       <c r="L5">
-        <v>4.044368600682594</v>
+        <v>-31.42857142857143</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -963,7 +969,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -972,79 +978,73 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.267</v>
+        <v>5.04</v>
       </c>
       <c r="V5">
-        <v>0.001461412151067324</v>
+        <v>0.1211538461538462</v>
       </c>
       <c r="W5">
-        <v>0.147940074906367</v>
+        <v>-0.1059490084985836</v>
       </c>
       <c r="X5">
-        <v>0.1234994215163031</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="Y5">
-        <v>0.02444065339006397</v>
+        <v>-0.1974244512504943</v>
       </c>
       <c r="Z5">
-        <v>0.03885683973211326</v>
+        <v>0.004116222760290557</v>
       </c>
       <c r="AA5">
-        <v>-0.03617971894857201</v>
+        <v>-0.1286751988931166</v>
       </c>
       <c r="AB5">
-        <v>0.122706924501364</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="AC5">
-        <v>-0.158886643449936</v>
+        <v>-0.2201506416450273</v>
       </c>
       <c r="AD5">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>1.893</v>
+        <v>-5.04</v>
       </c>
       <c r="AH5">
-        <v>0.01168451801363194</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.01276143211627083</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.01025499341795193</v>
+        <v>-0.137855579868709</v>
       </c>
       <c r="AK5">
-        <v>0.01120164740551384</v>
+        <v>-0.1835396941005098</v>
       </c>
       <c r="AL5">
-        <v>0.118</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>-14.982</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>-0.4052532833020638</v>
-      </c>
-      <c r="AO5">
-        <v>-48.13559322033898</v>
+        <v>-0</v>
       </c>
       <c r="AP5">
-        <v>-0.3551594746716698</v>
-      </c>
-      <c r="AQ5">
-        <v>0.3791216126017888</v>
+        <v>1.565217391304348</v>
       </c>
     </row>
     <row r="6">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="K6">
-        <v>-4.76</v>
+        <v>-3.54</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1088,31 +1088,31 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>16.9</v>
+        <v>14.2</v>
       </c>
       <c r="V6">
-        <v>0.1688311688311688</v>
+        <v>0.1197301854974705</v>
       </c>
       <c r="W6">
-        <v>-0.118407960199005</v>
+        <v>-0.07662337662337662</v>
       </c>
       <c r="X6">
-        <v>0.1226321919444638</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="Y6">
-        <v>-0.2410401521434687</v>
+        <v>-0.1680988193752873</v>
       </c>
       <c r="Z6">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>-0.1401232565682776</v>
+        <v>-0.1368600682593856</v>
       </c>
       <c r="AB6">
-        <v>0.1226321919444638</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="AC6">
-        <v>-0.2627554485127415</v>
+        <v>-0.2283355110112963</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-16.9</v>
+        <v>-14.2</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1133,25 +1133,25 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.203125</v>
+        <v>-0.1360153256704981</v>
       </c>
       <c r="AK6">
-        <v>-0.5633333333333332</v>
+        <v>-0.4781144781144781</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-0.019</v>
+        <v>-0.183</v>
       </c>
       <c r="AN6">
         <v>-0</v>
       </c>
       <c r="AP6">
-        <v>4.1320293398533</v>
+        <v>4</v>
       </c>
       <c r="AQ6">
-        <v>227.3684210526316</v>
+        <v>21.91256830601093</v>
       </c>
     </row>
     <row r="7">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aminex PLC (LSE:AEX)</t>
+          <t>Petrel Resources Plc (AIM:PET)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1170,26 +1170,8 @@
           <t>Oil/Gas (Production and Exploration)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.611</v>
-      </c>
-      <c r="G7">
-        <v>-19.63855421686747</v>
-      </c>
-      <c r="H7">
-        <v>-19.63855421686747</v>
-      </c>
-      <c r="I7">
-        <v>-88.43373493975903</v>
-      </c>
-      <c r="J7">
-        <v>-88.43373493975903</v>
-      </c>
       <c r="K7">
-        <v>-8.23</v>
-      </c>
-      <c r="L7">
-        <v>-99.1566265060241</v>
+        <v>-0.366</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1213,31 +1195,31 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>6.39</v>
+        <v>0.056</v>
       </c>
       <c r="V7">
-        <v>0.1172477064220183</v>
+        <v>0.008057553956834532</v>
       </c>
       <c r="W7">
-        <v>-0.20678391959799</v>
+        <v>-2.731343283582089</v>
       </c>
       <c r="X7">
-        <v>0.1226321919444638</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="Y7">
-        <v>-0.3294161115424538</v>
+        <v>-2.822818726334</v>
       </c>
       <c r="Z7">
-        <v>0.00210504958279439</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>-0.1861573968398894</v>
+        <v>-3.553398058252427</v>
       </c>
       <c r="AB7">
-        <v>0.1226321919444638</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="AC7">
-        <v>-0.3087895887843533</v>
+        <v>-3.644873501004338</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1249,7 +1231,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-6.39</v>
+        <v>-0.056</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1258,28 +1240,16 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.1328206194138433</v>
+        <v>-0.008123005512039455</v>
       </c>
       <c r="AK7">
-        <v>-0.2210307851954341</v>
+        <v>-1.866666666666667</v>
       </c>
       <c r="AL7">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>0.021</v>
-      </c>
-      <c r="AN7">
-        <v>-0</v>
-      </c>
-      <c r="AO7">
-        <v>-349.5238095238095</v>
-      </c>
-      <c r="AP7">
-        <v>4.376712328767123</v>
-      </c>
-      <c r="AQ7">
-        <v>-349.5238095238095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1290,7 +1260,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Petrel Resources Plc (AIM:PET)</t>
+          <t>Clontarf Energy plc (AIM:CLON)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1299,7 +1269,7 @@
         </is>
       </c>
       <c r="K8">
-        <v>-0.314</v>
+        <v>-0.694</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1323,31 +1293,22 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.031</v>
+        <v>0.484</v>
       </c>
       <c r="V8">
-        <v>0.01033333333333333</v>
+        <v>0.1406976744186046</v>
       </c>
       <c r="W8">
-        <v>-0.6193293885601577</v>
+        <v>0.5551999999999999</v>
       </c>
       <c r="X8">
-        <v>0.1226321919444638</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="Y8">
-        <v>-0.7419615805046216</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>-1.531707317073171</v>
+        <v>0.4637245572480892</v>
       </c>
       <c r="AB8">
-        <v>0.1226321919444638</v>
-      </c>
-      <c r="AC8">
-        <v>-1.654339509017634</v>
+        <v>0.09147544275191072</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1359,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>-0.031</v>
+        <v>-0.484</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -1368,10 +1329,10 @@
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>-0.01044122600202088</v>
+        <v>-0.1637347767253045</v>
       </c>
       <c r="AK8">
-        <v>-0.3009708737864077</v>
+        <v>-1.561290322580645</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1379,94 +1340,11 @@
       <c r="AM8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Clontarf Energy plc (AIM:CLON)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Oil/Gas (Production and Exploration)</t>
-        </is>
-      </c>
-      <c r="K9">
-        <v>-5.88</v>
-      </c>
-      <c r="M9">
-        <v>-0</v>
-      </c>
-      <c r="N9">
-        <v>-0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>-0</v>
-      </c>
-      <c r="Q9">
-        <v>-0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0.228</v>
-      </c>
-      <c r="V9">
-        <v>0.1288135593220339</v>
-      </c>
-      <c r="W9">
-        <v>158.9189189189189</v>
-      </c>
-      <c r="X9">
-        <v>0.1226321919444638</v>
-      </c>
-      <c r="Y9">
-        <v>158.7962867269745</v>
-      </c>
-      <c r="AB9">
-        <v>0.1226321919444638</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>-0.228</v>
-      </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>-0</v>
-      </c>
-      <c r="AJ9">
-        <v>-0.1478599221789883</v>
-      </c>
-      <c r="AK9">
-        <v>0.1542625169147497</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>-0.2534031413612565</v>
       </c>
     </row>
   </sheetData>
